--- a/data/LORRY_DAILY_PLANNING.xlsx
+++ b/data/LORRY_DAILY_PLANNING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\transport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014F3AAE-0E25-4EB8-8A29-8463818387B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840B8868-1A7F-48C6-AAA1-45BA0D92B2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
+    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
   <sheets>
     <sheet name="VIVIAN" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="TRANSPORT ROUTE" sheetId="6" r:id="rId6"/>
     <sheet name="ALL ROUTE" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MUATAN!$A$1:$F$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="152">
   <si>
     <t>NO</t>
   </si>
@@ -284,9 +287,6 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Message</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -498,6 +498,12 @@
   </si>
   <si>
     <t>TRANSPORT ROUTE</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
   </si>
 </sst>
 </file>
@@ -588,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +613,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -824,7 +854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -917,28 +947,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -968,6 +980,44 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1005,7 +1055,7 @@
   <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{E85DDC85-924C-4C03-A678-A3439F710EE8}" name="Number" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{AD8328CE-D3A6-4D50-94A2-1EF0233FFB18}" name="Code" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{CC540809-A48D-45B2-B43B-DB7573D9B567}" name="Message" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{CC540809-A48D-45B2-B43B-DB7573D9B567}" name="ROUTE" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1329,65 +1379,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D39D926-E7A0-4D94-A6B9-A8D9A8B3E680}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="11" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+    <row r="2" spans="1:11" s="11" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="42" t="s">
+      <c r="K2" s="34" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="33" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="40">
+      <c r="D3" s="33">
         <v>13377</v>
       </c>
       <c r="E3" s="4"/>
@@ -1400,23 +1450,23 @@
         <v>52</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="45">
+      <c r="J3" s="37">
         <f>F3/D3*100%</f>
         <v>0</v>
       </c>
-      <c r="K3" s="46"/>
-    </row>
-    <row r="4" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="38"/>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="33">
         <v>14164.5</v>
       </c>
       <c r="E4" s="4"/>
@@ -1427,23 +1477,23 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="45">
+      <c r="J4" s="37">
         <f t="shared" ref="J4:J12" si="1">F4/D4*100%</f>
         <v>0</v>
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="33">
         <v>13723.5</v>
       </c>
       <c r="E5" s="4"/>
@@ -1454,23 +1504,23 @@
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="45">
+      <c r="J5" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="33">
         <v>10027.5</v>
       </c>
       <c r="E6" s="4"/>
@@ -1483,23 +1533,23 @@
         <v>52</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="45">
+      <c r="J6" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="46"/>
-    </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="33" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="33">
         <v>10384.5</v>
       </c>
       <c r="E7" s="4"/>
@@ -1512,23 +1562,23 @@
         <v>52</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="45">
+      <c r="J7" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="46"/>
-    </row>
-    <row r="8" spans="1:11" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="38"/>
+    </row>
+    <row r="8" spans="1:11" s="42" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="39" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="39">
         <v>4620</v>
       </c>
       <c r="E8" s="3"/>
@@ -1539,23 +1589,23 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="48">
+      <c r="J8" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="49"/>
-    </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="33" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="33">
         <v>4368</v>
       </c>
       <c r="E9" s="4"/>
@@ -1568,23 +1618,23 @@
         <v>52</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="45">
+      <c r="J9" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="46"/>
-    </row>
-    <row r="10" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K9" s="38"/>
+    </row>
+    <row r="10" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="33">
         <v>4200</v>
       </c>
       <c r="E10" s="4"/>
@@ -1597,23 +1647,23 @@
         <v>52</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="45">
+      <c r="J10" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="46"/>
-    </row>
-    <row r="11" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="38"/>
+    </row>
+    <row r="11" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="33" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="33">
         <v>1144.5</v>
       </c>
       <c r="E11" s="4"/>
@@ -1626,19 +1676,19 @@
         <v>52</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="45">
+      <c r="J11" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="46"/>
-    </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="38"/>
+    </row>
+    <row r="12" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="40"/>
+      <c r="D12" s="33"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4">
@@ -1647,13 +1697,13 @@
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="45" t="e">
+      <c r="J12" s="37" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="46"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K12" s="38"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
       <c r="I16" s="18" t="s">
         <v>52</v>
       </c>
@@ -1666,23 +1716,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEDE0C5-2A47-4471-88E7-341CFFF617B6}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="26.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:11" s="11" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="26.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:11" s="11" customFormat="1" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +1767,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12">
         <v>1</v>
       </c>
@@ -1752,7 +1802,7 @@
       </c>
       <c r="K3" s="27"/>
     </row>
-    <row r="4" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1787,7 +1837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1822,7 +1872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1857,7 +1907,7 @@
       </c>
       <c r="K6" s="25"/>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1892,7 +1942,7 @@
       </c>
       <c r="K7" s="25"/>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -1921,7 +1971,7 @@
       </c>
       <c r="K8" s="28"/>
     </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1956,7 +2006,7 @@
       </c>
       <c r="K9" s="25"/>
     </row>
-    <row r="10" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1991,7 +2041,7 @@
       </c>
       <c r="K10" s="25"/>
     </row>
-    <row r="11" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -2026,7 +2076,7 @@
       </c>
       <c r="K11" s="25"/>
     </row>
-    <row r="12" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" s="5" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>10</v>
       </c>
@@ -2061,7 +2111,7 @@
       </c>
       <c r="K12" s="26"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
       <c r="I16" s="18" t="s">
         <v>52</v>
       </c>
@@ -2077,583 +2127,591 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A4:E41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="31" t="s">
+    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="C1" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="E1" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="F1" s="30" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="B2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="37">
+      <c r="C2" s="46">
         <v>38000</v>
       </c>
-      <c r="C7" s="37">
+      <c r="D2" s="46">
         <v>6070</v>
       </c>
-      <c r="D7" s="37">
+      <c r="E2" s="46">
         <v>20000</v>
       </c>
-      <c r="E7" s="40">
+      <c r="F2" s="47">
         <v>21000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="46">
+        <v>25000</v>
+      </c>
+      <c r="D3" s="46">
+        <v>11150</v>
+      </c>
+      <c r="E3" s="46">
+        <f>C3-D3</f>
+        <v>13850</v>
+      </c>
+      <c r="F3" s="47">
+        <v>14542.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="37">
+      <c r="C4" s="46">
         <v>25000</v>
       </c>
-      <c r="C8" s="37">
+      <c r="D4" s="46">
         <v>11370</v>
       </c>
-      <c r="D8" s="37">
-        <f t="shared" ref="D8:D16" si="0">B8-C8</f>
+      <c r="E4" s="46">
+        <f>C4-D4</f>
         <v>13630</v>
       </c>
-      <c r="E8" s="40">
+      <c r="F4" s="47">
         <v>14311.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="37">
+      <c r="C5" s="46">
         <v>25000</v>
       </c>
-      <c r="C9" s="37">
+      <c r="D5" s="46">
         <v>11010</v>
       </c>
-      <c r="D9" s="37">
-        <f t="shared" si="0"/>
+      <c r="E5" s="46">
+        <f>C5-D5</f>
         <v>13990</v>
       </c>
-      <c r="E9" s="40">
+      <c r="F5" s="47">
         <v>14689.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="37">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="46">
+        <v>24000</v>
+      </c>
+      <c r="D6" s="46">
+        <v>11380</v>
+      </c>
+      <c r="E6" s="46">
+        <f>C6-D6</f>
+        <v>12620</v>
+      </c>
+      <c r="F6" s="47">
+        <v>13251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="46">
+        <v>19000</v>
+      </c>
+      <c r="D7" s="46">
+        <v>8750</v>
+      </c>
+      <c r="E7" s="46">
+        <f>C7-D7</f>
+        <v>10250</v>
+      </c>
+      <c r="F7" s="47">
+        <v>10762.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="46">
+        <v>7500</v>
+      </c>
+      <c r="D8" s="46">
+        <v>4170</v>
+      </c>
+      <c r="E8" s="46">
+        <f>C8-D8</f>
+        <v>3330</v>
+      </c>
+      <c r="F8" s="47">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="46">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="46">
+        <v>3280</v>
+      </c>
+      <c r="E9" s="46">
+        <f>C9-D9</f>
+        <v>1720</v>
+      </c>
+      <c r="F9" s="47">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="46">
+        <v>5000</v>
+      </c>
+      <c r="D10" s="46">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="46">
+        <f>C10-D10</f>
+        <v>2000</v>
+      </c>
+      <c r="F10" s="47">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="46">
+        <v>2800</v>
+      </c>
+      <c r="D11" s="46">
+        <v>1740</v>
+      </c>
+      <c r="E11" s="46">
+        <f>C11-D11</f>
+        <v>1060</v>
+      </c>
+      <c r="F11" s="47">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="49">
+        <v>7700</v>
+      </c>
+      <c r="D12" s="49">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="49">
+        <f>C12-D12</f>
+        <v>4000</v>
+      </c>
+      <c r="F12" s="50">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="49">
+        <v>7500</v>
+      </c>
+      <c r="D13" s="49">
+        <v>3910</v>
+      </c>
+      <c r="E13" s="49">
+        <f>C13-D13</f>
+        <v>3590</v>
+      </c>
+      <c r="F13" s="50">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="49">
+        <v>7500</v>
+      </c>
+      <c r="D14" s="49">
+        <v>3470</v>
+      </c>
+      <c r="E14" s="49">
+        <f>C14-D14</f>
+        <v>4030</v>
+      </c>
+      <c r="F14" s="50">
+        <v>4231.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="52">
+        <v>13500</v>
+      </c>
+      <c r="D15" s="52">
+        <v>5410</v>
+      </c>
+      <c r="E15" s="52">
+        <f>C15-D15</f>
+        <v>8090</v>
+      </c>
+      <c r="F15" s="53">
+        <v>8494.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="55">
+        <v>24000</v>
+      </c>
+      <c r="D16" s="55">
+        <v>11320</v>
+      </c>
+      <c r="E16" s="55">
+        <f>C16-D16</f>
+        <v>12680</v>
+      </c>
+      <c r="F16" s="56">
+        <v>13314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="55">
+        <v>14200</v>
+      </c>
+      <c r="D17" s="55">
+        <v>5950</v>
+      </c>
+      <c r="E17" s="55">
+        <f>C17-D17</f>
+        <v>8250</v>
+      </c>
+      <c r="F17" s="56">
+        <v>8662.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="55">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="55">
+        <v>3380</v>
+      </c>
+      <c r="E18" s="55">
+        <f>C18-D18</f>
+        <v>1620</v>
+      </c>
+      <c r="F18" s="56">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="58">
         <v>25000</v>
       </c>
-      <c r="C10" s="37">
-        <v>11150</v>
-      </c>
-      <c r="D10" s="37">
-        <f t="shared" si="0"/>
-        <v>13850</v>
-      </c>
-      <c r="E10" s="40">
-        <v>14542.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="37">
+      <c r="D19" s="58">
+        <v>11510</v>
+      </c>
+      <c r="E19" s="58">
+        <f>C19-D19</f>
+        <v>13490</v>
+      </c>
+      <c r="F19" s="59">
+        <v>14164.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="58">
         <v>24000</v>
       </c>
-      <c r="C11" s="37">
-        <v>11380</v>
-      </c>
-      <c r="D11" s="37">
-        <f t="shared" si="0"/>
-        <v>12620</v>
-      </c>
-      <c r="E11" s="40">
-        <v>13251</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="37">
+      <c r="D20" s="58">
+        <v>10930</v>
+      </c>
+      <c r="E20" s="58">
+        <f>C20-D20</f>
+        <v>13070</v>
+      </c>
+      <c r="F20" s="59">
+        <v>13723.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="58">
+        <v>24000</v>
+      </c>
+      <c r="D21" s="58">
+        <v>11260</v>
+      </c>
+      <c r="E21" s="58">
+        <f>C21-D21</f>
+        <v>12740</v>
+      </c>
+      <c r="F21" s="59">
+        <v>13377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="58">
         <v>19000</v>
       </c>
-      <c r="C12" s="37">
-        <v>8750</v>
-      </c>
-      <c r="D12" s="37">
-        <f t="shared" si="0"/>
-        <v>10250</v>
-      </c>
-      <c r="E12" s="40">
-        <v>10762.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="37">
+      <c r="D22" s="58">
+        <v>9450</v>
+      </c>
+      <c r="E22" s="58">
+        <f>C22-D22</f>
+        <v>9550</v>
+      </c>
+      <c r="F22" s="59">
+        <v>10027.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="58">
+        <v>19000</v>
+      </c>
+      <c r="D23" s="58">
+        <v>9110</v>
+      </c>
+      <c r="E23" s="58">
+        <f>C23-D23</f>
+        <v>9890</v>
+      </c>
+      <c r="F23" s="59">
+        <v>10384.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="58">
+        <v>8500</v>
+      </c>
+      <c r="D24" s="58">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="58">
+        <f>C24-D24</f>
+        <v>4400</v>
+      </c>
+      <c r="F24" s="59">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="58">
         <v>7500</v>
       </c>
-      <c r="C13" s="37">
-        <v>4170</v>
-      </c>
-      <c r="D13" s="37">
-        <f t="shared" si="0"/>
-        <v>3330</v>
-      </c>
-      <c r="E13" s="40">
+      <c r="D25" s="58">
+        <v>3340</v>
+      </c>
+      <c r="E25" s="58">
+        <f>C25-D25</f>
+        <v>4160</v>
+      </c>
+      <c r="F25" s="59">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="58">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="58">
+        <v>3530</v>
+      </c>
+      <c r="E26" s="58">
+        <f>C26-D26</f>
+        <v>1470</v>
+      </c>
+      <c r="F26" s="59">
         <v>4200</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="37">
-        <v>5000</v>
-      </c>
-      <c r="C14" s="37">
-        <v>3280</v>
-      </c>
-      <c r="D14" s="37">
-        <f t="shared" si="0"/>
-        <v>1720</v>
-      </c>
-      <c r="E14" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="37">
-        <v>5000</v>
-      </c>
-      <c r="C15" s="37">
-        <v>3000</v>
-      </c>
-      <c r="D15" s="37">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="E15" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="37">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="60">
         <v>2800</v>
       </c>
-      <c r="C16" s="37">
-        <v>1740</v>
-      </c>
-      <c r="D16" s="37">
-        <f t="shared" si="0"/>
-        <v>1060</v>
-      </c>
-      <c r="E16" s="40">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="41"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="41"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="37">
-        <v>24000</v>
-      </c>
-      <c r="C19" s="37">
-        <v>11260</v>
-      </c>
-      <c r="D19" s="37">
-        <f>B19-C19</f>
-        <v>12740</v>
-      </c>
-      <c r="E19" s="40">
-        <v>13377</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="37">
-        <v>25000</v>
-      </c>
-      <c r="C20" s="37">
-        <v>11510</v>
-      </c>
-      <c r="D20" s="37">
-        <f t="shared" ref="D20:D27" si="1">B20-C20</f>
-        <v>13490</v>
-      </c>
-      <c r="E20" s="40">
-        <v>14164.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="37">
-        <v>24000</v>
-      </c>
-      <c r="C21" s="37">
-        <v>10930</v>
-      </c>
-      <c r="D21" s="37">
-        <f t="shared" si="1"/>
-        <v>13070</v>
-      </c>
-      <c r="E21" s="40">
-        <v>13723.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="37">
-        <v>19000</v>
-      </c>
-      <c r="C22" s="37">
-        <v>9450</v>
-      </c>
-      <c r="D22" s="37">
-        <f t="shared" si="1"/>
-        <v>9550</v>
-      </c>
-      <c r="E22" s="40">
-        <v>10027.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="37">
-        <v>19000</v>
-      </c>
-      <c r="C23" s="37">
-        <v>9110</v>
-      </c>
-      <c r="D23" s="37">
-        <f t="shared" si="1"/>
-        <v>9890</v>
-      </c>
-      <c r="E23" s="40">
-        <v>10384.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="37">
-        <v>8500</v>
-      </c>
-      <c r="C24" s="37">
-        <v>4100</v>
-      </c>
-      <c r="D24" s="37">
-        <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="E24" s="40">
-        <v>4620</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="37">
-        <v>7500</v>
-      </c>
-      <c r="C25" s="37">
-        <v>3340</v>
-      </c>
-      <c r="D25" s="37">
-        <f t="shared" si="1"/>
-        <v>4160</v>
-      </c>
-      <c r="E25" s="40">
-        <v>4368</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="37">
-        <v>5000</v>
-      </c>
-      <c r="C26" s="37">
-        <v>3530</v>
-      </c>
-      <c r="D26" s="37">
-        <f t="shared" si="1"/>
-        <v>1470</v>
-      </c>
-      <c r="E26" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="37">
-        <v>2800</v>
-      </c>
-      <c r="C27" s="37">
+      <c r="D27" s="58">
         <v>1710</v>
       </c>
-      <c r="D27" s="37">
-        <f t="shared" si="1"/>
+      <c r="E27" s="58">
+        <f>C27-D27</f>
         <v>1090</v>
       </c>
-      <c r="E27" s="40">
+      <c r="F27" s="59">
         <v>1144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="41"/>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="41"/>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="37">
-        <v>24000</v>
-      </c>
-      <c r="C30" s="37">
-        <v>11320</v>
-      </c>
-      <c r="D30" s="37">
-        <f t="shared" ref="D30:D35" si="2">B30-C30</f>
-        <v>12680</v>
-      </c>
-      <c r="E30" s="40">
-        <v>13314</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="37">
-        <v>14200</v>
-      </c>
-      <c r="C31" s="37">
-        <v>5950</v>
-      </c>
-      <c r="D31" s="37">
-        <f t="shared" si="2"/>
-        <v>8250</v>
-      </c>
-      <c r="E31" s="40">
-        <v>8662.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="37">
-        <v>5000</v>
-      </c>
-      <c r="C32" s="37">
-        <v>3380</v>
-      </c>
-      <c r="D32" s="37">
-        <f t="shared" si="2"/>
-        <v>1620</v>
-      </c>
-      <c r="E32" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="35"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="41"/>
-    </row>
-    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="41"/>
-    </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="37">
-        <v>13500</v>
-      </c>
-      <c r="C35" s="37">
-        <v>5410</v>
-      </c>
-      <c r="D35" s="37">
-        <f t="shared" si="2"/>
-        <v>8090</v>
-      </c>
-      <c r="E35" s="40">
-        <v>8494.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="41"/>
-    </row>
-    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="41"/>
-    </row>
-    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="37">
-        <v>7500</v>
-      </c>
-      <c r="C38" s="37">
-        <v>3470</v>
-      </c>
-      <c r="D38" s="37">
-        <f t="shared" ref="D38:D39" si="3">B38-C38</f>
-        <v>4030</v>
-      </c>
-      <c r="E38" s="40">
-        <v>4231.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="37">
-        <v>7500</v>
-      </c>
-      <c r="C39" s="37">
-        <v>3910</v>
-      </c>
-      <c r="D39" s="37">
-        <f t="shared" si="3"/>
-        <v>3590</v>
-      </c>
-      <c r="E39" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="39">
-        <v>7700</v>
-      </c>
-      <c r="C40" s="37">
-        <v>3700</v>
-      </c>
-      <c r="D40" s="37">
-        <f>B40-C40</f>
-        <v>4000</v>
-      </c>
-      <c r="E40" s="40">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="34"/>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="32"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F27" xr:uid="{7B6BCE54-C981-4548-89F2-F4BCBA0CF9C7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F27">
+      <sortCondition ref="A1:A27"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2662,344 +2720,349 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376B93B6-7CD8-4B1C-BCCE-53C84FB0C94C}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3010,275 +3073,283 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C059BE9D-3E54-4CDA-9067-74F9F8812A38}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="66.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
       </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3289,132 +3360,140 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7476908D-3A9A-4301-9740-379B31A7722E}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3425,14 +3504,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC573920-40DC-4BED-BE6B-4B26A7F6E4E4}">
   <dimension ref="A1:C96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>77</v>
       </c>
@@ -3440,1047 +3519,1047 @@
         <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="51">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="43">
         <v>2</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="52" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="43">
+        <v>3</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="51">
-        <v>3</v>
-      </c>
-      <c r="B3" s="52" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="43">
+        <v>4</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="43">
+        <v>5</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="43">
+        <v>6</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="43">
+        <v>64</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="43">
+        <v>58</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="43">
+        <v>66</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="43">
+        <v>67</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="43">
+        <v>68</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="43">
+        <v>69</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
+        <v>70</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="43">
+        <v>71</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="43">
+        <v>72</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="43">
+        <v>73</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="43">
+        <v>74</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="43">
+        <v>75</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="43">
+        <v>76</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="43">
+        <v>77</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="43">
+        <v>78</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="43">
+        <v>79</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="43">
         <v>80</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="B23" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="43">
+        <v>81</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="43">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="51">
-        <v>4</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="52" t="s">
+      <c r="B25" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="43">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="51">
-        <v>5</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="52" t="s">
+      <c r="B26" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="43">
         <v>84</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="51">
-        <v>6</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="52" t="s">
+      <c r="B27" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="43">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="51">
-        <v>64</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="52" t="s">
+      <c r="B28" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="43">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="51">
-        <v>58</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="52" t="s">
+      <c r="B29" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="43">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="51">
-        <v>66</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="52" t="s">
+      <c r="B30" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="43">
         <v>88</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="51">
-        <v>67</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="52" t="s">
+      <c r="B31" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="43">
+        <v>45</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="43">
         <v>89</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="51">
-        <v>68</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="52" t="s">
+      <c r="B33" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="43">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="51">
-        <v>69</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="52" t="s">
+      <c r="B34" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="43">
+        <v>23</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="43">
+        <v>1</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="43">
+        <v>7</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="43">
+        <v>8</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="43">
+        <v>9</v>
+      </c>
+      <c r="B39" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="43">
+        <v>10</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="43">
+        <v>11</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="43">
+        <v>12</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="43">
+        <v>13</v>
+      </c>
+      <c r="B43" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="43">
+        <v>14</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="43">
+        <v>15</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="43">
+        <v>16</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="43">
+        <v>17</v>
+      </c>
+      <c r="B47" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="43">
+        <v>18</v>
+      </c>
+      <c r="B48" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="43">
+        <v>19</v>
+      </c>
+      <c r="B49" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="43">
+        <v>20</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="43">
+        <v>21</v>
+      </c>
+      <c r="B51" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="43">
+        <v>22</v>
+      </c>
+      <c r="B52" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="43">
+        <v>42</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="43">
+        <v>43</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="43">
+        <v>44</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="43">
+        <v>46</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="43">
+        <v>47</v>
+      </c>
+      <c r="B57" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="43">
+        <v>48</v>
+      </c>
+      <c r="B58" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="43">
+        <v>49</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="43">
+        <v>50</v>
+      </c>
+      <c r="B60" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="43">
+        <v>51</v>
+      </c>
+      <c r="B61" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="43">
+        <v>52</v>
+      </c>
+      <c r="B62" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="43">
+        <v>53</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="43">
+        <v>24</v>
+      </c>
+      <c r="B64" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C64" s="44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="43">
+        <v>25</v>
+      </c>
+      <c r="B65" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="43">
+        <v>26</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="43">
+        <v>27</v>
+      </c>
+      <c r="B67" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="43">
+        <v>62</v>
+      </c>
+      <c r="B68" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="43">
+        <v>63</v>
+      </c>
+      <c r="B69" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="43">
+        <v>28</v>
+      </c>
+      <c r="B70" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="43">
+        <v>39</v>
+      </c>
+      <c r="B71" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="43">
+        <v>29</v>
+      </c>
+      <c r="B72" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="43">
+        <v>40</v>
+      </c>
+      <c r="B73" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="43">
+        <v>30</v>
+      </c>
+      <c r="B74" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="43">
+        <v>41</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="43">
+        <v>31</v>
+      </c>
+      <c r="B76" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="43">
+        <v>32</v>
+      </c>
+      <c r="B77" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="43">
+        <v>60</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="43">
+        <v>61</v>
+      </c>
+      <c r="B79" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="43">
+        <v>33</v>
+      </c>
+      <c r="B80" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="43">
+        <v>34</v>
+      </c>
+      <c r="B81" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="43">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="51">
-        <v>70</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="52" t="s">
+      <c r="B82" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="43">
+        <v>35</v>
+      </c>
+      <c r="B83" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="43">
+        <v>36</v>
+      </c>
+      <c r="B84" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="43">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="51">
-        <v>71</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="52" t="s">
+      <c r="B85" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="44" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="43">
+        <v>54</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="44" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="43">
+        <v>57</v>
+      </c>
+      <c r="B87" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87" s="44" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="43">
+        <v>59</v>
+      </c>
+      <c r="B88" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="43">
+        <v>56</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="43">
+        <v>55</v>
+      </c>
+      <c r="B90" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="43">
+        <v>65</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="43">
+        <v>37</v>
+      </c>
+      <c r="B92" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="43">
+        <v>38</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="43">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="51">
-        <v>72</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="52" t="s">
+      <c r="B94" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="43">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="51">
-        <v>73</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="51">
-        <v>74</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="51">
-        <v>75</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="51">
-        <v>76</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="51">
-        <v>77</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="51">
-        <v>78</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="51">
-        <v>79</v>
-      </c>
-      <c r="B22" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="51">
-        <v>80</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="51">
-        <v>81</v>
-      </c>
-      <c r="B24" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="51">
-        <v>82</v>
-      </c>
-      <c r="B25" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="51">
-        <v>83</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="51">
-        <v>84</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="51">
-        <v>85</v>
-      </c>
-      <c r="B28" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="51">
-        <v>86</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="51">
-        <v>87</v>
-      </c>
-      <c r="B30" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="52" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="51">
-        <v>88</v>
-      </c>
-      <c r="B31" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="52" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="51">
-        <v>45</v>
-      </c>
-      <c r="B32" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="52" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="51">
-        <v>89</v>
-      </c>
-      <c r="B33" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="52" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="51">
-        <v>90</v>
-      </c>
-      <c r="B34" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="52" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="51">
-        <v>23</v>
-      </c>
-      <c r="B35" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" s="52" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="51">
-        <v>1</v>
-      </c>
-      <c r="B36" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="51">
-        <v>7</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="51">
-        <v>8</v>
-      </c>
-      <c r="B38" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="51">
-        <v>9</v>
-      </c>
-      <c r="B39" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="51">
-        <v>10</v>
-      </c>
-      <c r="B40" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="51">
-        <v>11</v>
-      </c>
-      <c r="B41" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="51">
-        <v>12</v>
-      </c>
-      <c r="B42" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="51">
-        <v>13</v>
-      </c>
-      <c r="B43" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="51">
-        <v>14</v>
-      </c>
-      <c r="B44" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="51">
-        <v>15</v>
-      </c>
-      <c r="B45" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="51">
-        <v>16</v>
-      </c>
-      <c r="B46" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="51">
-        <v>17</v>
-      </c>
-      <c r="B47" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="51">
-        <v>18</v>
-      </c>
-      <c r="B48" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="51">
-        <v>19</v>
-      </c>
-      <c r="B49" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="51">
-        <v>20</v>
-      </c>
-      <c r="B50" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="51">
-        <v>21</v>
-      </c>
-      <c r="B51" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="51">
-        <v>22</v>
-      </c>
-      <c r="B52" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="51">
-        <v>42</v>
-      </c>
-      <c r="B53" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="51">
-        <v>43</v>
-      </c>
-      <c r="B54" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="51">
-        <v>44</v>
-      </c>
-      <c r="B55" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="51">
-        <v>46</v>
-      </c>
-      <c r="B56" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="51">
-        <v>47</v>
-      </c>
-      <c r="B57" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="51">
-        <v>48</v>
-      </c>
-      <c r="B58" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C58" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="51">
-        <v>49</v>
-      </c>
-      <c r="B59" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="51">
-        <v>50</v>
-      </c>
-      <c r="B60" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C60" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="51">
-        <v>51</v>
-      </c>
-      <c r="B61" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="51">
-        <v>52</v>
-      </c>
-      <c r="B62" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="51">
-        <v>53</v>
-      </c>
-      <c r="B63" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="51">
-        <v>24</v>
-      </c>
-      <c r="B64" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C64" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="51">
-        <v>25</v>
-      </c>
-      <c r="B65" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" s="52" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="51">
-        <v>26</v>
-      </c>
-      <c r="B66" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="51">
-        <v>27</v>
-      </c>
-      <c r="B67" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67" s="52" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="51">
-        <v>62</v>
-      </c>
-      <c r="B68" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C68" s="52" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="51">
-        <v>63</v>
-      </c>
-      <c r="B69" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69" s="52" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="51">
-        <v>28</v>
-      </c>
-      <c r="B70" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" s="52" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="51">
-        <v>39</v>
-      </c>
-      <c r="B71" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" s="52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="51">
-        <v>29</v>
-      </c>
-      <c r="B72" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="52" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="51">
-        <v>40</v>
-      </c>
-      <c r="B73" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="52" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="51">
-        <v>30</v>
-      </c>
-      <c r="B74" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="52" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="51">
-        <v>41</v>
-      </c>
-      <c r="B75" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="51">
-        <v>31</v>
-      </c>
-      <c r="B76" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="52" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="51">
-        <v>32</v>
-      </c>
-      <c r="B77" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="52" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="51">
-        <v>60</v>
-      </c>
-      <c r="B78" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" s="52" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="51">
-        <v>61</v>
-      </c>
-      <c r="B79" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="52" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="51">
-        <v>33</v>
-      </c>
-      <c r="B80" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="52" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="51">
-        <v>34</v>
-      </c>
-      <c r="B81" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C81" s="52" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="51">
-        <v>91</v>
-      </c>
-      <c r="B82" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="52" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="51">
-        <v>35</v>
-      </c>
-      <c r="B83" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="51">
-        <v>36</v>
-      </c>
-      <c r="B84" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="51">
-        <v>92</v>
-      </c>
-      <c r="B85" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" s="52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="51">
-        <v>54</v>
-      </c>
-      <c r="B86" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" s="52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="51">
-        <v>57</v>
-      </c>
-      <c r="B87" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" s="52" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="51">
-        <v>59</v>
-      </c>
-      <c r="B88" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88" s="52" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="51">
-        <v>56</v>
-      </c>
-      <c r="B89" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C89" s="52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="51">
-        <v>55</v>
-      </c>
-      <c r="B90" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C90" s="52" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="51">
-        <v>65</v>
-      </c>
-      <c r="B91" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C91" s="52" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="51">
-        <v>37</v>
-      </c>
-      <c r="B92" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C92" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="51">
-        <v>38</v>
-      </c>
-      <c r="B93" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C93" s="52" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="51">
-        <v>93</v>
-      </c>
-      <c r="B94" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C94" s="52" t="s">
+      <c r="B95" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="44" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="51">
-        <v>94</v>
-      </c>
-      <c r="B95" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C95" s="52" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="51"/>
-      <c r="B96" s="52"/>
-      <c r="C96" s="52"/>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="43"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/LORRY_DAILY_PLANNING.xlsx
+++ b/data/LORRY_DAILY_PLANNING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B4584-4FF7-4A02-924D-40B6E3AE5CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136690E0-A7BD-46F4-9879-82C699D16ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
   <sheets>
     <sheet name="VIVIAN" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="158">
   <si>
     <t>NO</t>
   </si>
@@ -502,6 +502,9 @@
     <t>MON</t>
   </si>
   <si>
+    <t>TEUS</t>
+  </si>
+  <si>
     <t>WED</t>
   </si>
   <si>
@@ -517,14 +520,14 @@
     <t>SUN</t>
   </si>
   <si>
-    <t>TUE</t>
+    <t>NAME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,13 +541,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -604,8 +600,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,6 +647,36 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -709,101 +758,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -813,6 +854,49 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1176,330 +1260,330 @@
   <dimension ref="A2:K16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="16" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="15" style="16" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="26.5546875" style="16" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="42" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="16"/>
+    <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="15" style="12" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="17" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20">
+    <row r="3" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="11">
+      <c r="C3" s="16"/>
+      <c r="D3" s="7">
         <v>13377</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16">
         <f>D3-F3</f>
         <v>13377</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="28">
+      <c r="I3" s="16"/>
+      <c r="J3" s="24">
         <f>F3/D3*100%</f>
         <v>0</v>
       </c>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20">
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>14164.5</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16">
         <f t="shared" ref="G4:G12" si="0">D4-F4</f>
         <v>14164.5</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="28">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="24">
         <f t="shared" ref="J4:J12" si="1">F4/D4*100%</f>
         <v>0</v>
       </c>
-      <c r="K4" s="20"/>
-    </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20">
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>13723.5</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
         <v>13723.5</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="28">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20">
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="7">
         <v>10027.5</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16">
         <f>D6-F6</f>
         <v>10027.5</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="28">
+      <c r="I6" s="16"/>
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20">
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="7">
         <v>10384.5</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
         <v>10384.5</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="28">
+      <c r="I7" s="16"/>
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:11" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <v>4620</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>4620</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="31">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20">
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="7">
         <v>4368</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20">
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16">
         <f>D6-F9</f>
         <v>10027.5</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="28">
+      <c r="I9" s="16"/>
+      <c r="J9" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="29"/>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20">
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>4200</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="28">
+      <c r="I10" s="16"/>
+      <c r="J10" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
+      <c r="K10" s="25"/>
+    </row>
+    <row r="11" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="7">
         <v>1144.5</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20">
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
         <v>1144.5</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="28">
+      <c r="I11" s="16"/>
+      <c r="J11" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
         <v>10</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="28" t="e">
+      <c r="H12" s="18"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="29"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="20" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1513,435 +1597,435 @@
   <dimension ref="A2:K16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="16" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17" style="16" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="33.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="16"/>
+    <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="17" style="12" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="33.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="17" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="20">
+    <row r="3" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="17">
         <v>21000</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="16">
         <v>4</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="16">
         <v>21110</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="16">
         <f>D3-F3</f>
         <v>-110</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="24">
         <f>F3/D3*100%</f>
         <v>1.0052380952380953</v>
       </c>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="33">
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="29">
         <v>2</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="30">
         <v>14311.5</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33">
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29">
         <f t="shared" ref="G4:G13" si="0">D4-F4</f>
         <v>14311.5</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="36">
+      <c r="H4" s="31"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="32">
         <f t="shared" ref="J4:J7" si="1">F4/D4*100%</f>
         <v>0</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="29" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20">
+    <row r="5" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="17">
         <v>14689.5</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <v>4</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="16">
         <v>14156</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
         <v>533.5</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>0.96368154123693794</v>
       </c>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="20">
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16">
         <v>4</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="17">
         <v>14542.5</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <v>7</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <v>13962</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="16">
         <f t="shared" si="0"/>
         <v>580.5</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>0.96008251676121714</v>
       </c>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="20">
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="16">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="17">
         <v>13251</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="16">
         <v>4</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="16">
         <v>14610</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
         <v>-1359</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>1.1025582974869821</v>
       </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:11" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="17">
         <v>10762.5</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="15">
         <v>15</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="15">
         <v>12479</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <f t="shared" si="0"/>
         <v>-1716.5</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="27">
         <f t="shared" ref="J8:J13" si="2">F8/D8*100%</f>
         <v>1.1594889663182346</v>
       </c>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="20">
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="16">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="17">
         <v>4200</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="16">
         <v>5</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="16">
         <v>5440</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="16">
         <f t="shared" si="0"/>
         <v>-1240</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="24">
         <f t="shared" si="2"/>
         <v>1.2952380952380953</v>
       </c>
-      <c r="K9" s="29"/>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20">
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="16">
         <v>8</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="17">
         <v>4200</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="16">
         <v>7</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="16">
         <v>5155</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
         <v>-955</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="24">
         <f t="shared" si="2"/>
         <v>1.2273809523809525</v>
       </c>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20">
+      <c r="K10" s="25"/>
+    </row>
+    <row r="11" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="16">
         <v>9</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="16">
         <v>1113</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="16">
         <v>3</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="16">
         <v>1181</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
         <v>-68</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="24">
         <f t="shared" si="2"/>
         <v>1.0610961365678346</v>
       </c>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="16">
         <v>10</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="17">
         <v>8662.5</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="16">
         <v>14</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="16">
         <v>8936</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="16">
         <f t="shared" si="0"/>
         <v>-273.5</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="24">
         <f t="shared" si="2"/>
         <v>1.0315728715728716</v>
       </c>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" spans="1:11" s="37" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
+      <c r="K12" s="25"/>
+    </row>
+    <row r="13" spans="1:11" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16">
         <v>11</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="16">
         <v>4200</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="16">
         <v>6</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="16">
         <v>5559</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="16">
         <f t="shared" si="0"/>
         <v>-1359</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="24">
         <f t="shared" si="2"/>
         <v>1.3235714285714286</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="K13" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="20" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1956,581 +2040,676 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A4:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="5"/>
+    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C1" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D1" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E1" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F1" s="43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10">
+      <c r="C2" s="45">
         <v>38000</v>
       </c>
-      <c r="C7" s="10">
+      <c r="D2" s="45">
         <v>6070</v>
       </c>
-      <c r="D7" s="10">
+      <c r="E2" s="45">
         <v>20000</v>
       </c>
-      <c r="E7" s="11">
+      <c r="F2" s="46">
         <v>21000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="45">
+        <v>25000</v>
+      </c>
+      <c r="D3" s="45">
+        <v>11150</v>
+      </c>
+      <c r="E3" s="45">
+        <f t="shared" ref="E3:E27" si="0">C3-D3</f>
+        <v>13850</v>
+      </c>
+      <c r="F3" s="46">
+        <v>14542.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10">
+      <c r="C4" s="45">
         <v>25000</v>
       </c>
-      <c r="C8" s="10">
+      <c r="D4" s="45">
         <v>11370</v>
       </c>
-      <c r="D8" s="10">
-        <f t="shared" ref="D8:D16" si="0">B8-C8</f>
+      <c r="E4" s="45">
+        <f t="shared" si="0"/>
         <v>13630</v>
       </c>
-      <c r="E8" s="11">
+      <c r="F4" s="46">
         <v>14311.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10">
+      <c r="C5" s="45">
         <v>25000</v>
       </c>
-      <c r="C9" s="10">
+      <c r="D5" s="45">
         <v>11010</v>
       </c>
-      <c r="D9" s="10">
+      <c r="E5" s="45">
         <f t="shared" si="0"/>
         <v>13990</v>
       </c>
-      <c r="E9" s="11">
+      <c r="F5" s="46">
         <v>14689.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="10">
-        <v>25000</v>
-      </c>
-      <c r="C10" s="10">
-        <v>11150</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>13850</v>
-      </c>
-      <c r="E10" s="11">
-        <v>14542.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10">
+      <c r="C6" s="45">
         <v>24000</v>
       </c>
-      <c r="C11" s="10">
+      <c r="D6" s="45">
         <v>11380</v>
       </c>
-      <c r="D11" s="10">
+      <c r="E6" s="45">
         <f t="shared" si="0"/>
         <v>12620</v>
       </c>
-      <c r="E11" s="11">
+      <c r="F6" s="46">
         <v>13251</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10">
+      <c r="C7" s="45">
         <v>19000</v>
       </c>
-      <c r="C12" s="10">
+      <c r="D7" s="45">
         <v>8750</v>
       </c>
-      <c r="D12" s="10">
+      <c r="E7" s="45">
         <f t="shared" si="0"/>
         <v>10250</v>
       </c>
-      <c r="E12" s="11">
+      <c r="F7" s="46">
         <v>10762.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="10">
+      <c r="C8" s="45">
         <v>7500</v>
       </c>
-      <c r="C13" s="10">
+      <c r="D8" s="45">
         <v>4170</v>
       </c>
-      <c r="D13" s="10">
+      <c r="E8" s="45">
         <f t="shared" si="0"/>
         <v>3330</v>
       </c>
-      <c r="E13" s="11">
+      <c r="F8" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="10">
+      <c r="C9" s="45">
         <v>5000</v>
       </c>
-      <c r="C14" s="10">
+      <c r="D9" s="45">
         <v>3280</v>
       </c>
-      <c r="D14" s="10">
+      <c r="E9" s="45">
         <f t="shared" si="0"/>
         <v>1720</v>
       </c>
-      <c r="E14" s="11">
+      <c r="F9" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="10">
+      <c r="C10" s="45">
         <v>5000</v>
       </c>
-      <c r="C15" s="10">
+      <c r="D10" s="45">
         <v>3000</v>
       </c>
-      <c r="D15" s="10">
+      <c r="E10" s="45">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="F10" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="10">
+      <c r="C11" s="45">
         <v>2800</v>
       </c>
-      <c r="C16" s="10">
+      <c r="D11" s="45">
         <v>1740</v>
       </c>
-      <c r="D16" s="10">
+      <c r="E11" s="45">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="E16" s="11">
+      <c r="F11" s="46">
         <v>1113</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="48">
+        <v>7700</v>
+      </c>
+      <c r="D12" s="48">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="48">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="F12" s="49">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="48">
+        <v>7500</v>
+      </c>
+      <c r="D13" s="48">
+        <v>3910</v>
+      </c>
+      <c r="E13" s="48">
+        <f t="shared" si="0"/>
+        <v>3590</v>
+      </c>
+      <c r="F13" s="49">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="48">
+        <v>7500</v>
+      </c>
+      <c r="D14" s="48">
+        <v>3470</v>
+      </c>
+      <c r="E14" s="48">
+        <f t="shared" si="0"/>
+        <v>4030</v>
+      </c>
+      <c r="F14" s="49">
+        <v>4231.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="51">
+        <v>13500</v>
+      </c>
+      <c r="D15" s="51">
+        <v>5410</v>
+      </c>
+      <c r="E15" s="51">
+        <f t="shared" si="0"/>
+        <v>8090</v>
+      </c>
+      <c r="F15" s="52">
+        <v>8494.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="54">
+        <v>24000</v>
+      </c>
+      <c r="D16" s="54">
+        <v>11320</v>
+      </c>
+      <c r="E16" s="54">
+        <f t="shared" si="0"/>
+        <v>12680</v>
+      </c>
+      <c r="F16" s="55">
+        <v>13314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="54">
+        <v>14200</v>
+      </c>
+      <c r="D17" s="54">
+        <v>5950</v>
+      </c>
+      <c r="E17" s="54">
+        <f t="shared" si="0"/>
+        <v>8250</v>
+      </c>
+      <c r="F17" s="55">
+        <v>8662.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="54">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="54">
+        <v>3380</v>
+      </c>
+      <c r="E18" s="54">
+        <f t="shared" si="0"/>
+        <v>1620</v>
+      </c>
+      <c r="F18" s="55">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="B19" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="57">
+        <v>25000</v>
+      </c>
+      <c r="D19" s="57">
+        <v>11510</v>
+      </c>
+      <c r="E19" s="57">
+        <f t="shared" si="0"/>
+        <v>13490</v>
+      </c>
+      <c r="F19" s="58">
+        <v>14164.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="57">
+        <v>24000</v>
+      </c>
+      <c r="D20" s="57">
+        <v>10930</v>
+      </c>
+      <c r="E20" s="57">
+        <f t="shared" si="0"/>
+        <v>13070</v>
+      </c>
+      <c r="F20" s="58">
+        <v>13723.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="10">
+      <c r="C21" s="57">
         <v>24000</v>
       </c>
-      <c r="C19" s="10">
+      <c r="D21" s="57">
         <v>11260</v>
       </c>
-      <c r="D19" s="10">
-        <f>B19-C19</f>
+      <c r="E21" s="57">
+        <f t="shared" si="0"/>
         <v>12740</v>
       </c>
-      <c r="E19" s="11">
+      <c r="F21" s="58">
         <v>13377</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="10">
-        <v>25000</v>
-      </c>
-      <c r="C20" s="10">
-        <v>11510</v>
-      </c>
-      <c r="D20" s="10">
-        <f t="shared" ref="D20:D27" si="1">B20-C20</f>
-        <v>13490</v>
-      </c>
-      <c r="E20" s="11">
-        <v>14164.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="10">
-        <v>24000</v>
-      </c>
-      <c r="C21" s="10">
-        <v>10930</v>
-      </c>
-      <c r="D21" s="10">
-        <f t="shared" si="1"/>
-        <v>13070</v>
-      </c>
-      <c r="E21" s="11">
-        <v>13723.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="10">
+      <c r="C22" s="57">
         <v>19000</v>
       </c>
-      <c r="C22" s="10">
+      <c r="D22" s="57">
         <v>9450</v>
       </c>
-      <c r="D22" s="10">
-        <f t="shared" si="1"/>
+      <c r="E22" s="57">
+        <f t="shared" si="0"/>
         <v>9550</v>
       </c>
-      <c r="E22" s="11">
+      <c r="F22" s="58">
         <v>10027.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="10">
+      <c r="C23" s="57">
         <v>19000</v>
       </c>
-      <c r="C23" s="10">
+      <c r="D23" s="57">
         <v>9110</v>
       </c>
-      <c r="D23" s="10">
-        <f t="shared" si="1"/>
+      <c r="E23" s="57">
+        <f t="shared" si="0"/>
         <v>9890</v>
       </c>
-      <c r="E23" s="11">
+      <c r="F23" s="58">
         <v>10384.5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="10">
+      <c r="C24" s="57">
         <v>8500</v>
       </c>
-      <c r="C24" s="10">
+      <c r="D24" s="57">
         <v>4100</v>
       </c>
-      <c r="D24" s="10">
-        <f t="shared" si="1"/>
+      <c r="E24" s="57">
+        <f t="shared" si="0"/>
         <v>4400</v>
       </c>
-      <c r="E24" s="11">
+      <c r="F24" s="58">
         <v>4620</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="10">
+      <c r="C25" s="57">
         <v>7500</v>
       </c>
-      <c r="C25" s="10">
+      <c r="D25" s="57">
         <v>3340</v>
       </c>
-      <c r="D25" s="10">
-        <f t="shared" si="1"/>
+      <c r="E25" s="57">
+        <f t="shared" si="0"/>
         <v>4160</v>
       </c>
-      <c r="E25" s="11">
+      <c r="F25" s="58">
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="10">
+      <c r="C26" s="57">
         <v>5000</v>
       </c>
-      <c r="C26" s="10">
+      <c r="D26" s="57">
         <v>3530</v>
       </c>
-      <c r="D26" s="10">
-        <f t="shared" si="1"/>
+      <c r="E26" s="57">
+        <f t="shared" si="0"/>
         <v>1470</v>
       </c>
-      <c r="E26" s="11">
+      <c r="F26" s="58">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="10">
+      <c r="C27" s="59">
         <v>2800</v>
       </c>
-      <c r="C27" s="10">
+      <c r="D27" s="57">
         <v>1710</v>
       </c>
-      <c r="D27" s="10">
-        <f t="shared" si="1"/>
+      <c r="E27" s="57">
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="E27" s="11">
+      <c r="F27" s="58">
         <v>1144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="10">
-        <v>24000</v>
-      </c>
-      <c r="C30" s="10">
-        <v>11320</v>
-      </c>
-      <c r="D30" s="10">
-        <f t="shared" ref="D30:D35" si="2">B30-C30</f>
-        <v>12680</v>
-      </c>
-      <c r="E30" s="11">
-        <v>13314</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="10">
-        <v>14200</v>
-      </c>
-      <c r="C31" s="10">
-        <v>5950</v>
-      </c>
-      <c r="D31" s="10">
-        <f t="shared" si="2"/>
-        <v>8250</v>
-      </c>
-      <c r="E31" s="11">
-        <v>8662.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="10">
-        <v>5000</v>
-      </c>
-      <c r="C32" s="10">
-        <v>3380</v>
-      </c>
-      <c r="D32" s="10">
-        <f t="shared" si="2"/>
-        <v>1620</v>
-      </c>
-      <c r="E32" s="11">
-        <v>4200</v>
-      </c>
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="12"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="10">
-        <v>13500</v>
-      </c>
-      <c r="C35" s="10">
-        <v>5410</v>
-      </c>
-      <c r="D35" s="10">
-        <f t="shared" si="2"/>
-        <v>8090</v>
-      </c>
-      <c r="E35" s="11">
-        <v>8494.5</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="12"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="12"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="10">
-        <v>7500</v>
-      </c>
-      <c r="C38" s="10">
-        <v>3470</v>
-      </c>
-      <c r="D38" s="10">
-        <f t="shared" ref="D38:D39" si="3">B38-C38</f>
-        <v>4030</v>
-      </c>
-      <c r="E38" s="11">
-        <v>4231.5</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="10">
-        <v>7500</v>
-      </c>
-      <c r="C39" s="10">
-        <v>3910</v>
-      </c>
-      <c r="D39" s="10">
-        <f t="shared" si="3"/>
-        <v>3590</v>
-      </c>
-      <c r="E39" s="11">
-        <v>4200</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="14">
-        <v>7700</v>
-      </c>
-      <c r="C40" s="10">
-        <v>3700</v>
-      </c>
-      <c r="D40" s="10">
-        <f>B40-C40</f>
-        <v>4000</v>
-      </c>
-      <c r="E40" s="11">
-        <v>4200</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="15"/>
+      <c r="E41" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3164,24 +3343,24 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="39">
+      <c r="A27" s="35">
         <v>68</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="38" t="s">
+      <c r="B27" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="34" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="41">
+      <c r="A28" s="37">
         <v>90</v>
       </c>
-      <c r="B28" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="43" t="s">
+      <c r="B28" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="39" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4411,41 +4590,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
       <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
         <v>156</v>
       </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="41" t="s">
         <v>106</v>
       </c>
       <c r="B3" t="s">
@@ -4465,7 +4644,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="41" t="s">
         <v>107</v>
       </c>
       <c r="B4" t="s">
@@ -4485,7 +4664,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="41" t="s">
         <v>108</v>
       </c>
       <c r="B5" t="s">
@@ -4502,7 +4681,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="41" t="s">
         <v>111</v>
       </c>
       <c r="B6" t="s">
@@ -4519,7 +4698,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="41" t="s">
         <v>112</v>
       </c>
       <c r="B7" t="s">
@@ -4536,7 +4715,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="41" t="s">
         <v>115</v>
       </c>
       <c r="B8" t="s">
@@ -4553,7 +4732,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="41" t="s">
         <v>116</v>
       </c>
       <c r="B9" t="s">
@@ -4567,7 +4746,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="41" t="s">
         <v>117</v>
       </c>
       <c r="B10" t="s">
@@ -4581,7 +4760,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="41" t="s">
         <v>119</v>
       </c>
       <c r="B11" t="s">
@@ -4595,7 +4774,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="41" t="s">
         <v>120</v>
       </c>
       <c r="B12" t="s">
@@ -4603,7 +4782,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B13" t="s">
@@ -4611,7 +4790,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="41" t="s">
         <v>118</v>
       </c>
       <c r="B14" t="s">
@@ -4650,37 +4829,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
       <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
